--- a/training_menu_master.xlsx
+++ b/training_menu_master.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1278" uniqueCount="641">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1323" uniqueCount="670">
   <si>
     <t xml:space="preserve">menu_id</t>
   </si>
@@ -2796,65 +2796,149 @@
     <t xml:space="preserve">先読みと判断</t>
   </si>
   <si>
-    <t xml:space="preserve">打たれる前にコースを宣言してシュートストップ</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">コースを予測して声に出す</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">シュートを受ける</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">宣言とのズレを確認</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">「打つ前に言えた？」</t>
-  </si>
-  <si>
-    <t xml:space="preserve">予測精度・宣言回数</t>
-  </si>
-  <si>
-    <t xml:space="preserve">予測の外在化</t>
+    <t xml:space="preserve">シュートを受ける前に「どこへ来るか」を声に出して宣言し、予測の精度を確かめる。</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">キッカーが蹴る前に「左寄り」「右足で低い弾道」などを宣言</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">実際のシュートとのズレを言語化する</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">本連続で宣言し、予測精度（正解率）を記録する</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">疲労後に同じ課題を繰り返し、精度の変化を確認する</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">宣言と結果のズレに注目させる。「予測できた」ではなく「なぜそう思った？」を問い返す</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">宣言一致率（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">本中何本か）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">宣言の根拠が具体的か</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">疲労後に精度が落ちるか</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">予測を「外に出す」ことで内部モデルが可視化され、ズレを修正できる速度が上がる</t>
   </si>
   <si>
     <t xml:space="preserve">POS-GK-002</t>
@@ -2866,65 +2950,129 @@
     <t xml:space="preserve">落下予測の精度</t>
   </si>
   <si>
-    <t xml:space="preserve">クロス上がった瞬間に着地点を宣言</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">クロスが上がる</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">着地点を宣言する</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">実際の着地と比較</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">「ボールが上がった瞬間に言えた？」</t>
-  </si>
-  <si>
-    <t xml:space="preserve">予測と着地のズレ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">軌道モデルの更新</t>
+    <t xml:space="preserve">クロスボールが上がった瞬間に着地点を宣言し、落下予測の精度を高める。</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ボールが蹴り出された瞬間に「ファーポスト前方」「ニアで落ちる」などを宣言</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">実際の落下点との誤差を確認する</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">蹴る選手を変えて多様なクロスに対応する</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">宣言してキャッチ／コーチングをセットで行う</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">「上がった瞬間に言えた？」を確認。後から言うのは</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">NG</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">宣言のタイミング（上がった瞬間か）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">落下点の誤差（近距離・遠距離別）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">「軌跡の感覚入力」と「予測」のズレを繰り返し修正することで、落下モデルが精密になる</t>
   </si>
   <si>
     <t xml:space="preserve">POS-GK-003</t>
@@ -2957,65 +3105,148 @@
     <t xml:space="preserve">不確実性の判断</t>
   </si>
   <si>
-    <t xml:space="preserve">助走・目線から飛ぶ方向を論理的に判断</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">キッカーの助走を観察</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">傾向データを収集</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">飛ぶ方向を決める</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">「何を見て決めた？」</t>
-  </si>
-  <si>
-    <t xml:space="preserve">正答率・根拠の明確さ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ベイズ的判断</t>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PK</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">場面での「飛ぶ方向判断」を情報に基づいて行う。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">キッカーの助走角度・目線・体の向きを観察し、傾向を事前に把握</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">「右・左・中央」の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">択で判断根拠を宣言してから飛ぶ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">「どの手がかりが最も有効だったか」を後から振り返る</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">「根拠なしのギャンブル」と「情報に基づく判断」を区別させる</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">根拠の明確さ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">正解率よりも判断プロセスの質</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">手がかりの特定精度</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">不確実性が高いほど、情報を最大限に使った合理的な判断が重要になる</t>
   </si>
   <si>
     <t xml:space="preserve">POS-GK-004</t>
@@ -3064,65 +3295,223 @@
     <t xml:space="preserve">角度の圧縮</t>
   </si>
   <si>
-    <t xml:space="preserve">相手の選択肢を制限するポジション取り</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">相手の位置を確認</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">角度を計算</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">最適ポジションへ移動</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">「今の位置で角度は消えている？」</t>
-  </si>
-  <si>
-    <t xml:space="preserve">角度の最小化</t>
-  </si>
-  <si>
-    <t xml:space="preserve">能動的な不確実性圧縮</t>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">GK</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">が「シュートコースを最も狭める位置」を宣言してから動く。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FW</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">がボールを持って向かってくる</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|GK</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">は「今の最適ポジションは○○」と声に出してから前に出る</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|FW</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">がシュートを打ちにくい状況を作れているか確認する</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">コーチは</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">GK</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">の出るタイミング（早すぎ・遅すぎ）をフィードバック</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">「最小化できている？」「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">GK</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">が来て</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FW</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">は何を感じた？」と問い返す</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">出るタイミングの適切さ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|FW</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">の選択肢が実際に減っているか</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ポジションの正確さ</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">相手の選択肢を予測し、不確実性をこちらから圧縮する能動的な判断が求められる</t>
   </si>
   <si>
     <t xml:space="preserve">POS-GK-005</t>
@@ -3445,65 +3834,206 @@
     <t xml:space="preserve">相手の意図を読む</t>
   </si>
   <si>
-    <t xml:space="preserve">相手の体の動きから方向転換を予測</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">相手の体の動きを観察</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">方向転換を予測</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">身体を先に動かす</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">「体のどこを見ている？」</t>
-  </si>
-  <si>
-    <t xml:space="preserve">予測の先読み率</t>
-  </si>
-  <si>
-    <t xml:space="preserve">相手モデルの更新</t>
+    <t xml:space="preserve">相手がドリブルで仕掛けてくる際、「どちらに切る」かを体の向きから予測・宣言する。</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">アタッカーがボールを持ちながら</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">DF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">に向かってくる</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|DF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">は相手の肩・腰・体重移動を見て「右に切る」などを事前に宣言</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">実際の方向との一致率を記録する（目標：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">本中</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">本以上）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">「どの手がかりで予測したか」を毎回言語化する</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">「宣言後に動いた？　宣言せずに動いた？」を分けて評価する</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">宣言一致率（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">本中</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">本以上が目標）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">手がかりの言語化ができているか</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">相手の体の動きから相手の意図を逆推定する能力を磨くことで、先手を取れるようになる</t>
   </si>
   <si>
     <t xml:space="preserve">POS-DF-002</t>
@@ -3515,62 +4045,168 @@
     <t xml:space="preserve">先に体を置く</t>
   </si>
   <si>
-    <t xml:space="preserve">パスラインを予測して先に体を置く練習</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">パスコースを予測</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">先にポジションを取る</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">実際のパスと比較</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">「読むより先に動いた？」</t>
-  </si>
-  <si>
-    <t xml:space="preserve">インターセプト率</t>
+    <t xml:space="preserve">相手がパスを出す前に、出てくるパスコースを予測してポジションを取る。</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">相手ボール保持者を観察し「次のパス先」を指差しで宣言</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">そのパスラインを切れる位置に先に動く（待たない）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">予測が外れたときは「どの情報を見逃したか」を振り返る</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">対</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">のミニゲームで「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">つ先のパスを先読みして動く」を課題とする</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">「読むより先に動いた？」「待ってから動いた？」を区別</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">インターセプト率</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">先にポジションを取れている回数</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">予測の根拠の言語化</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">パスラインを「読む」のではなく「予測して先に体を置く」ことで不確実性を圧縮できる</t>
   </si>
   <si>
     <t xml:space="preserve">POS-DF-003</t>
@@ -3589,6 +4225,175 @@
         <rFont val="DejaVu Sans"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">プレスをかけるタイミング（行く</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">待つ）を、根拠とともに声に出してから動く。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">相手がボールを受けた瞬間「今すぐ行く」「少し待つ」を宣言</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">宣言の根拠（「相手のコントロールが大きかった」など）を同時に言語化</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">プレスの成功</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">失敗後に「タイミングは正しかったか」を問い返す</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">チームでプレス発動ルールを共有し、全員で宣言を習慣化</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">根拠のない行動と根拠のある行動を徹底的に区別させる</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">宣言とプレスの一致</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">タイミング判断の根拠の質</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">チームとの連動率</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">「行く</t>
     </r>
     <r>
@@ -3608,66 +4413,8 @@
         <rFont val="DejaVu Sans"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">待つ」の判断を声に出して確認</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">状況を観察</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">「行く」または「待つ」を宣言</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">実際に行動</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">「なぜ今だと判断した？」</t>
-  </si>
-  <si>
-    <t xml:space="preserve">判断の適切さ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">能動的な判断</t>
+      <t xml:space="preserve">待つ」の判断は、相手の状態の不確実性を低く見積もれた瞬間を能動的に選ぶ行為</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">POS-DF-004</t>
@@ -3679,6 +4426,15 @@
     <t xml:space="preserve">集団の同期</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ライン上げ</t>
+    </r>
     <r>
       <rPr>
         <sz val="9"/>
@@ -3687,144 +4443,17 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">DF</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">ラインの組織的な押し上げを練習</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">ラインの高さを確認</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">全員で一斉に動く</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">コミュニケーション</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">「全員の動きが合っている？」</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ラインの統一性</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POS-DF-005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ステップワーク（バックペダル）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">身体の向きの維持</t>
-  </si>
-  <si>
-    <t xml:space="preserve">後退しながら相手に正対するステップ練習</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">バックペダルの形を確認</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">相手と向き合いながら後退</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">体の向きを保つ</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">「相手から目を離さない」</t>
-  </si>
-  <si>
-    <t xml:space="preserve">身体制御の精度</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POS-DF-006</t>
-  </si>
-  <si>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">下げのタイミングを</t>
+    </r>
     <r>
       <rPr>
         <sz val="9"/>
@@ -3833,90 +4462,267 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">1v1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">ディフェンス</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">選択肢の制限</t>
-  </si>
-  <si>
-    <t xml:space="preserve">コースを切りながら相手の選択肢を制限</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">相手の選択肢を確認</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">コースを切る</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">誘導して奪う</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">「相手に何を選ばせる？」</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ボール奪取率</t>
-  </si>
-  <si>
-    <t xml:space="preserve">能動的な選択肢圧縮</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POS-DF-007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">カバーリングポジション</t>
-  </si>
-  <si>
-    <t xml:space="preserve">連携のカバー</t>
+      <t xml:space="preserve">DF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ラインで統一し、共有された判断モデルを構築する。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">リーダー</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">DF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">が「ライン上げ」「ライン下げ」を声で宣言してから動く</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">他の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">DF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">がそれに合わせる（声なしでも動けるようになることが目標）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">オフサイドトラップの成功</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">失敗を記録し、タイミングのズレを分析</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">「なぜそのタイミングで上げたか」を毎回説明できるようにする</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">「全員の動きが合っている？」「声なしで合わせられたか？」</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ラインの統一性</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">オフサイドトラップ成功率</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">タイミング説明の質</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">チームとして共有された予測モデルが揃うほど、集団として一体的な動きができる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POS-DF-005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ステップワーク（バックペダル）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">身体の向きの維持</t>
+  </si>
+  <si>
+    <t xml:space="preserve">後退しながら相手に正対するステップ練習</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">バックペダルの形を確認</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">相手と向き合いながら後退</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">体の向きを保つ</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">「相手から目を離さない」</t>
+  </si>
+  <si>
+    <t xml:space="preserve">身体制御の精度</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POS-DF-006</t>
   </si>
   <si>
     <r>
@@ -3927,285 +4733,90 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">DF</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">ラインのカバーシャドウを反復</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">チームメイトのポジションを確認</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">カバー位置を取る</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">連携して守る</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">「カバーに入れている？」</t>
-  </si>
-  <si>
-    <t xml:space="preserve">カバーリングの適切さ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">協調的な防御</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POS-DF-008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">インターセプト練習</t>
-  </si>
-  <si>
-    <t xml:space="preserve">先読みカット</t>
-  </si>
-  <si>
-    <t xml:space="preserve">パスコースを予測して先読みカット</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">相手のパスコースを予測</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">先に体を動かす</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">カットする</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">「予測して先に動いた？」</t>
-  </si>
-  <si>
-    <t xml:space="preserve">予測的行動</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POS-MF-001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ファーストタッチ前の選択宣言</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">受ける前に次のプレーを宣言してから受ける</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">ボールが来る前に宣言</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">その通りに動く</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">振り返り</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">「受ける前に決まっていた？」</t>
-  </si>
-  <si>
-    <t xml:space="preserve">事前宣言の成功率</t>
-  </si>
-  <si>
-    <t xml:space="preserve">先行判断の速度</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POS-MF-002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">プレス方向予測と回避ルート選択</t>
-  </si>
-  <si>
-    <t xml:space="preserve">認知負荷の軽減</t>
-  </si>
-  <si>
-    <t xml:space="preserve">プレスの方向を事前に確率として持つ</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">プレスの来る方向を予測</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">回避ルートを選ぶ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">実際に比較</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">「来る前に予測できた？」</t>
-  </si>
-  <si>
-    <t xml:space="preserve">回避成功率</t>
-  </si>
-  <si>
-    <t xml:space="preserve">確率的な予測</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POS-MF-003</t>
+      <t xml:space="preserve">1v1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ディフェンス</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">選択肢の制限</t>
+  </si>
+  <si>
+    <t xml:space="preserve">コースを切りながら相手の選択肢を制限</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">相手の選択肢を確認</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">コースを切る</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">誘導して奪う</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">「相手に何を選ばせる？」</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ボール奪取率</t>
+  </si>
+  <si>
+    <t xml:space="preserve">能動的な選択肢圧縮</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POS-DF-007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">カバーリングポジション</t>
+  </si>
+  <si>
+    <t xml:space="preserve">連携のカバー</t>
   </si>
   <si>
     <r>
@@ -4216,23 +4827,418 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">つの選択肢の優先順位付け</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">並列判断</t>
-  </si>
-  <si>
-    <t xml:space="preserve">複数の選択肢を並列で持って意思決定</t>
+      <t xml:space="preserve">DF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ラインのカバーシャドウを反復</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">チームメイトのポジションを確認</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">カバー位置を取る</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">連携して守る</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">「カバーに入れている？」</t>
+  </si>
+  <si>
+    <t xml:space="preserve">カバーリングの適切さ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">協調的な防御</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POS-DF-008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">インターセプト練習</t>
+  </si>
+  <si>
+    <t xml:space="preserve">先読みカット</t>
+  </si>
+  <si>
+    <t xml:space="preserve">パスコースを予測して先読みカット</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">相手のパスコースを予測</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">先に体を動かす</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">カットする</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">「予測して先に動いた？」</t>
+  </si>
+  <si>
+    <t xml:space="preserve">インターセプト率</t>
+  </si>
+  <si>
+    <t xml:space="preserve">予測的行動</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POS-MF-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ファーストタッチ前の選択宣言</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ボールが来る前に「受けたら何をするか」を宣言してからファーストタッチを行う。</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">パスが届く前に「右足でコントロールして前へ」などを宣言</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">宣言通りに実行できたか、変更が必要だったかを振り返る</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">変更が必要だった場合、「何の情報が来て変えたか」を言語化</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">人でのポゼッション練習でルールとして導入する</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">「受ける前に決まっていた？」「何で変えた？」を問う</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">事前宣言の成功率</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">変更理由の言語化</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">宣言習慣の定着度</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">ファーストタッチ前に選択を確定させることで、実行と修正のサイクルを最速にできる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POS-MF-002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">プレス方向予測と回避ルート選択</t>
+  </si>
+  <si>
+    <t xml:space="preserve">認知負荷の軽減</t>
+  </si>
+  <si>
+    <t xml:space="preserve">相手のプレス方向を予測し、最も効率的な回避ルートを瞬時に判断する。</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">相手プレス役がどの方向から来るかを「足の向き」で予測して宣言</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">その予測に基づき、「体の向き」を先に作っておく</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">プレスが来た方向と予測の一致率を記録する</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">逆プレスをかけられた場合の「次の手」も準備しておく</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">「来る前に予測できた？」「体の向きは先に作れていた？」</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">予測一致率</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">体の向きの準備タイミング</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">逆プレス対応の成功率</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">プレスの方向を事前に「確率」として持っておくことで認知負荷が下がる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POS-MF-003</t>
   </si>
   <si>
     <r>
@@ -4252,7 +5258,89 @@
         <rFont val="DejaVu Sans"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">つの選択肢を確認</t>
+      <t xml:space="preserve">つの選択肢の優先順位付け</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">並列判断</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ボールを受ける前に「第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">の選択肢」を頭の中で準備しておく。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ボールを受ける前に周囲をスキャンし、選択肢を</t>
     </r>
     <r>
       <rPr>
@@ -4262,16 +5350,16 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">優先順位を声に出す</t>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">つ挙げる</t>
     </r>
     <r>
       <rPr>
@@ -4290,436 +5378,8 @@
         <rFont val="DejaVu Sans"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">実行</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">「なぜその順番？」</t>
-  </si>
-  <si>
-    <t xml:space="preserve">判断の速さと質</t>
-  </si>
-  <si>
-    <t xml:space="preserve">並列的な意思決定</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POS-MF-004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">守備→攻撃切り替えタイミング予測</t>
-  </si>
-  <si>
-    <t xml:space="preserve">切り替えの速さ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">「次の状態」を予測して素早く転換</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">ボールを奪う</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">次の攻撃を予測する</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">素早く切り替える</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">「奪う前から次を考えている？」</t>
-  </si>
-  <si>
-    <t xml:space="preserve">先の状態の予測</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POS-MF-005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ボールリテンション（ロンド）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ポゼッション維持</t>
-  </si>
-  <si>
-    <t xml:space="preserve">パスコースを作り続けるポゼッション練習</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">ロンドの形を作る</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">常に動いてパスコースを作る</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">ボールを保持</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">「パスコースを作っている？」</t>
-  </si>
-  <si>
-    <t xml:space="preserve">協調的なパスコース形成</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POS-MF-006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ターンとリリース</t>
-  </si>
-  <si>
-    <t xml:space="preserve">プレッシャー下での展開</t>
-  </si>
-  <si>
-    <t xml:space="preserve">プレッシャーを受けながら素早くターンして展開</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">プレッシャーを設定</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">ターンのタイミングを計る</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">素早く展開</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">「ターン前に次を決めた？」</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ターンの成功率</t>
-  </si>
-  <si>
-    <t xml:space="preserve">状況適応</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POS-MF-007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">縦パスの差し込み</t>
-  </si>
-  <si>
-    <t xml:space="preserve">縦への展開</t>
-  </si>
-  <si>
-    <t xml:space="preserve">縦パスのタイミングを繰り返し練習</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">縦のコースを確認</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">タイミングを計る</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">縦パスを差し込む</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">「なぜ今？」</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POS-MF-008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ゲームリード練習</t>
-  </si>
-  <si>
-    <t xml:space="preserve">試合のコントロール</t>
-  </si>
-  <si>
-    <t xml:space="preserve">テンポをコントロールする意識を持ったボール保持</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">試合のテンポを設定</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">ボールを保持しながら状況を見る</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">テンポを変える</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">「今はどんな展開が必要？」</t>
-  </si>
-  <si>
-    <t xml:space="preserve">テンポの適切さ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ゲームモデルの構築</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POS-FW-001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ゾーン選択型シュートドリル</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fw</t>
-  </si>
-  <si>
-    <t xml:space="preserve">コース選択</t>
-  </si>
-  <si>
-    <t xml:space="preserve">シュートゾーンを宣言してから打つ練習</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">ゾーンを設定</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">コースを宣言</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">シュートする</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">「宣言通りに打てた？」</t>
-  </si>
-  <si>
-    <t xml:space="preserve">意図的なシュート選択</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POS-FW-002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">裏抜けタイミングの予測ドリル</t>
-  </si>
-  <si>
-    <t xml:space="preserve">タイミングの精度</t>
-  </si>
-  <si>
+      <t xml:space="preserve">「最優先は右前方のスペース、次は左の味方」などを声で宣言</t>
+    </r>
     <r>
       <rPr>
         <sz val="9"/>
@@ -4728,19 +5388,17 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">DF</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">の背後への抜け出しタイミングを反復</t>
-    </r>
-  </si>
-  <si>
+      <t xml:space="preserve">|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">プレー後に「どの選択肢を使ったか、なぜか」を振り返る</t>
+    </r>
     <r>
       <rPr>
         <sz val="9"/>
@@ -4749,16 +5407,810 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">DF</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">の動きを観察</t>
+      <t xml:space="preserve">|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">使わなかった選択肢の「その時点での状況」も確認する</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">つ挙げられた？」「なぜ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">番を選んだ？」</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">選択肢の数と質</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">選択理由の明確さ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">プレー後の振り返り精度</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">複数の選択肢を並列で持つことで、不確実な状況での意思決定速度が上がる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POS-MF-004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">守備→攻撃切り替えタイミング予測</t>
+  </si>
+  <si>
+    <t xml:space="preserve">切り替えの速さ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ボールロスト直後から奪取の瞬間まで、「切り替え完了のタイミング」を予測して動く。</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">守備から攻撃に切り替わる瞬間を「予測」してスプリント開始</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">「次のプレーで取れそうか」を常に</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">秒先まで予測して動き続ける</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">切り替えが遅れた場面を記録し、「どの情報を見落としたか」を分析</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">チームとして「切り替えの共通サイン」を決めて練習する</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">「奪う前から次を考えていた？」「何を見落とした？」</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">切り替えのタイミング</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">情報見落としの言語化</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">チームサインの定着度</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">切り替えの速さは「次の状態を予測する速さ」に等しい。常に先のシナリオを更新し続ける</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POS-MF-005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ボールリテンション（ロンド）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ポゼッション維持</t>
+  </si>
+  <si>
+    <t xml:space="preserve">パスコースを作り続けるポゼッション練習</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ロンドの形を作る</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">常に動いてパスコースを作る</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ボールを保持</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">「パスコースを作っている？」</t>
+  </si>
+  <si>
+    <t xml:space="preserve">協調的なパスコース形成</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POS-MF-006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ターンとリリース</t>
+  </si>
+  <si>
+    <t xml:space="preserve">プレッシャー下での展開</t>
+  </si>
+  <si>
+    <t xml:space="preserve">プレッシャーを受けながら素早くターンして展開</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">プレッシャーを設定</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ターンのタイミングを計る</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">素早く展開</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">「ターン前に次を決めた？」</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ターンの成功率</t>
+  </si>
+  <si>
+    <t xml:space="preserve">状況適応</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POS-MF-007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">縦パスの差し込み</t>
+  </si>
+  <si>
+    <t xml:space="preserve">縦への展開</t>
+  </si>
+  <si>
+    <t xml:space="preserve">縦パスのタイミングを繰り返し練習</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">縦のコースを確認</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">タイミングを計る</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">縦パスを差し込む</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">「なぜ今？」</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POS-MF-008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ゲームリード練習</t>
+  </si>
+  <si>
+    <t xml:space="preserve">試合のコントロール</t>
+  </si>
+  <si>
+    <t xml:space="preserve">テンポをコントロールする意識を持ったボール保持</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">試合のテンポを設定</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ボールを保持しながら状況を見る</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">テンポを変える</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">「今はどんな展開が必要？」</t>
+  </si>
+  <si>
+    <t xml:space="preserve">テンポの適切さ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ゲームモデルの構築</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POS-FW-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ゾーン選択型シュートドリル</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fw</t>
+  </si>
+  <si>
+    <t xml:space="preserve">コース選択</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">シュートを打つ前に</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">GK</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">の体勢とゴールのゾーンを評価し、最適なコースを選ぶ。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ゴールを</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ゾーンに分割し、シュート前に「どのゾーンを狙うか」を宣言</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|GK</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">の重心・手の位置から「空いているゾーン」を瞬時に判断</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">宣言したゾーンと実際の着弾点のズレを記録する</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">GK</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">が来る前に蹴れたか・来てから蹴ったか」もチェック</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">「宣言通りに打てた？」「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">GK</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">のどこを見て決めた？」</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">コース精度（宣言と着弾の一致）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|GK</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">を見た判断の正確さ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">タイミングの適切さ</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">GK</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">の位置を情報源として予測を更新しながら、最適コースを選ぶ</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">POS-FW-002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">裏抜けタイミングの予測ドリル</t>
+  </si>
+  <si>
+    <t xml:space="preserve">タイミングの精度</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">パスが出るタイミングを予測して「</t>
     </r>
     <r>
       <rPr>
@@ -4768,16 +6220,16 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">抜け出すタイミングを予測</t>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">拍早く」動き出す。</t>
     </r>
     <r>
       <rPr>
@@ -4787,31 +6239,28 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">スプリント</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">「ぎりぎりのタイミングを狙えた？」</t>
-  </si>
-  <si>
-    <t xml:space="preserve">オフサイドにならない抜け出し率</t>
-  </si>
-  <si>
-    <t xml:space="preserve">タイミング予測</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POS-FW-003</t>
-  </si>
-  <si>
+      <t xml:space="preserve">DF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ラインを予測的に突破する。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">パスを出す選手の「予備動作（体の向き・視線）」を観察する</t>
+    </r>
     <r>
       <rPr>
         <sz val="9"/>
@@ -4820,16 +6269,16 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">対</t>
+      <t xml:space="preserve">|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">「今出る」と判断した根拠を声に出してから動き出す</t>
     </r>
     <r>
       <rPr>
@@ -4839,19 +6288,17 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">フィニッシュ選択</t>
-    </r>
-  </si>
-  <si>
+      <t xml:space="preserve">|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">オフサイドの場合は「どのタイミングが早すぎたか」を振り返る</t>
+    </r>
     <r>
       <rPr>
         <sz val="9"/>
@@ -4860,17 +6307,104 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">GK</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">との</t>
-    </r>
+      <t xml:space="preserve">|DF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ラインの高さを事前にチェックし、走るコースを予測的に決める</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">「ぎりぎりのタイミングを狙えた？」「何を見て動いた？」</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">オフサイドにならない抜け出し率</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">動き出しの根拠の明確さ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|DF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ライン読みの精度</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">裏抜けは</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">DF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">と出し手の両方を読んで、その隙間のタイミングを探す二重の予測行動</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">POS-FW-003</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="9"/>
@@ -4879,10 +6413,17 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">1v1</t>
-    </r>
-  </si>
-  <si>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">対</t>
+    </r>
     <r>
       <rPr>
         <sz val="9"/>
@@ -4891,16 +6432,16 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">GK</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">の位置を見てコースを選択</t>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">フィニッシュ選択</t>
     </r>
   </si>
   <si>
@@ -4921,7 +6462,7 @@
         <rFont val="DejaVu Sans"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">の位置を確認</t>
+      <t xml:space="preserve">との</t>
     </r>
     <r>
       <rPr>
@@ -4931,17 +6472,10 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">コースを選択</t>
-    </r>
+      <t xml:space="preserve">1v1</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="9"/>
@@ -4950,36 +6484,6 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">シュートする</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">「</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
       <t xml:space="preserve">GK</t>
     </r>
     <r>
@@ -4989,55 +6493,8 @@
         <rFont val="DejaVu Sans"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">のどこが空いている？」</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">シュート成功率</t>
-  </si>
-  <si>
-    <t xml:space="preserve">状況判断</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POS-FW-004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">オフザボール動き出し予測</t>
-  </si>
-  <si>
-    <t xml:space="preserve">スペースの創出</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">パスを受ける前の動き出しで</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">DF</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">をずらす</t>
-    </r>
-  </si>
-  <si>
+      <t xml:space="preserve">と</t>
+    </r>
     <r>
       <rPr>
         <sz val="9"/>
@@ -5046,16 +6503,16 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">DF</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">のポジションを観察</t>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">対</t>
     </r>
     <r>
       <rPr>
@@ -5065,17 +6522,19 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">動き出しのタイミングを計る</t>
-    </r>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">の局面で「いつシュートを打つか・どのコースか」を意識的に判断する。</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="9"/>
@@ -5084,204 +6543,17 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">スペースを作る</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">「</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">DF</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">をずらせた？」</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">スペース創出の成功率</t>
-  </si>
-  <si>
-    <t xml:space="preserve">協調的な動き出し</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POS-FW-005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ポストプレー</t>
-  </si>
-  <si>
-    <t xml:space="preserve">身体を使ったキープ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">身体を当ててキープしながら落とす</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">ボールを受ける</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">身体でキープ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">味方へ落とす</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">「キープ中に次を見られている？」</t>
-  </si>
-  <si>
-    <t xml:space="preserve">キープ成功率</t>
-  </si>
-  <si>
-    <t xml:space="preserve">身体感覚と協調</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POS-FW-006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">クロスへの入り方</t>
-  </si>
-  <si>
-    <t xml:space="preserve">動き出しのパターン</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ファー・ニアへの動き出しパターン練習</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">クロスが上がるタイミングを予測</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">動き出しの方向を選択</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">合わせる</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">「いつ・どっちへ動いた？」</t>
-  </si>
-  <si>
-    <t xml:space="preserve">合わせる成功率</t>
-  </si>
-  <si>
-    <t xml:space="preserve">動き出しの予測</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POS-FW-007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">プレッシング始動</t>
-  </si>
-  <si>
-    <t xml:space="preserve">守備のスイッチ</t>
-  </si>
-  <si>
+      <t xml:space="preserve">GK</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">が前に出てきた「歩数」をカウントし、最適な打ち時を判断</t>
+    </r>
     <r>
       <rPr>
         <sz val="9"/>
@@ -5290,89 +6562,17 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">FW</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">からのプレスでチームの守備を起動</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">プレスのタイミングを設定</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">チームへのサインを出す</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">全員で連動</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">「チームがついてきた？」</t>
-  </si>
-  <si>
-    <t xml:space="preserve">プレスの連動率</t>
-  </si>
-  <si>
-    <t xml:space="preserve">集団的な守備行動</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POS-FW-008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">スペースメイキング</t>
-  </si>
-  <si>
-    <t xml:space="preserve">味方のためのスペース</t>
-  </si>
-  <si>
-    <t xml:space="preserve">味方のスペースを作るための動き出し</t>
-  </si>
-  <si>
+      <t xml:space="preserve">|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">「シュートを打つ」か「さらに持ち込む」かを事前に基準を決める</t>
+    </r>
     <r>
       <rPr>
         <sz val="9"/>
@@ -5381,16 +6581,16 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">DF</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">の引き付けを意識</t>
+      <t xml:space="preserve">|GK</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">が倒れたら→浮かせる、</t>
     </r>
     <r>
       <rPr>
@@ -5400,16 +6600,16 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="DejaVu Sans"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">スペースを作る動きをする</t>
+      <t xml:space="preserve">GK</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">が立っていたら→コースを狙う</t>
     </r>
     <r>
       <rPr>
@@ -5428,6 +6628,597 @@
         <rFont val="DejaVu Sans"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">成功・失敗後に「その時点での</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">GK</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">の状態」を言語化する</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">GK</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">のどこを見て決めた？」「なぜそのタイミング？」</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">シュート成功率</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|GK</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">の状態の言語化</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">判断の迷いが少ないか</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">GK</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">の状態を情報として取り込み、最も確率の高い結末に向けて行動を最適化する</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">POS-FW-004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">オフザボール動き出し予測</t>
+  </si>
+  <si>
+    <t xml:space="preserve">スペースの創出</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ボールを持っていない時間に「次にボールが来るシーン」を予測して有利な位置を取る。</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ボールが味方の足元に入った瞬間、「次に自分が受ける場面」を予測して動き出す</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">動き出す方向を指差しで宣言し、出し手に意思を伝える</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">「パスが来なかった場合」も、その原因を分析して次の動きに活かす</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">チームとして「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FW</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">が動き出したら</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">MF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">が見る」という習慣を作る</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">「誰のためのスペース？」「動いた意図を出し手に伝えられた？」</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">スペース創出の成功率</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">出し手への意思伝達</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">チーム習慣の定着度</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">オフザボールの動き出しは、チームの未来の状態を先に予測して形作る能動的な行動</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POS-FW-005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ポストプレー</t>
+  </si>
+  <si>
+    <t xml:space="preserve">身体を使ったキープ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">身体を当ててキープしながら落とす</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ボールを受ける</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">身体でキープ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">味方へ落とす</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">「キープ中に次を見られている？」</t>
+  </si>
+  <si>
+    <t xml:space="preserve">キープ成功率</t>
+  </si>
+  <si>
+    <t xml:space="preserve">身体感覚と協調</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POS-FW-006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">クロスへの入り方</t>
+  </si>
+  <si>
+    <t xml:space="preserve">動き出しのパターン</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ファー・ニアへの動き出しパターン練習</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">クロスが上がるタイミングを予測</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">動き出しの方向を選択</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">合わせる</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">「いつ・どっちへ動いた？」</t>
+  </si>
+  <si>
+    <t xml:space="preserve">合わせる成功率</t>
+  </si>
+  <si>
+    <t xml:space="preserve">動き出しの予測</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POS-FW-007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">プレッシング始動</t>
+  </si>
+  <si>
+    <t xml:space="preserve">守備のスイッチ</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FW</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">からのプレスでチームの守備を起動</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">プレスのタイミングを設定</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">チームへのサインを出す</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">全員で連動</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">「チームがついてきた？」</t>
+  </si>
+  <si>
+    <t xml:space="preserve">プレスの連動率</t>
+  </si>
+  <si>
+    <t xml:space="preserve">集団的な守備行動</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POS-FW-008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">スペースメイキング</t>
+  </si>
+  <si>
+    <t xml:space="preserve">味方のためのスペース</t>
+  </si>
+  <si>
+    <t xml:space="preserve">味方のスペースを作るための動き出し</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">DF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">の引き付けを意識</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">スペースを作る動きをする</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">味方が使えたか確認</t>
     </r>
   </si>
@@ -5439,6 +7230,610 @@
   </si>
   <si>
     <t xml:space="preserve">協調的な空間創出</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AG-GEN-033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ポジショナルプレー分析</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ポジションの理解</t>
+  </si>
+  <si>
+    <t xml:space="preserve">映像または図解を使い、攻守のポジション配置を確認・修正する。</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">映像</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">or</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ホワイトボードで試合場面を再現</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">「今どこにいるべきか」を全員で確認</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">修正ポイントを</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">つに絞って共有</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">次の練習でその修正を意識して取り組む</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">「なぜその位置？」を問い続ける。答えられることが目標</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ポジション理解の正確さ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">修正の定着度</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">次の練習への接続</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">空間モデルの共有と更新</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AG-GEN-034</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">対</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">フリーマン</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">フリーマンの活用</t>
+  </si>
+  <si>
+    <t xml:space="preserve">フリーマン（常に攻撃側）を使うタイミングを予測し、パスコースを広げる判断を養う。</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">対</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">にフリーマン</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">人を追加してゲーム</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">フリーマンを使うタイミングを自分で判断</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">「なぜ今フリーマンを使った</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">使わなかった？」を振り返る</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">フリーマン活用率を記録する</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">「フリーマンが見えているか？」「どのタイミングで使う？」</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">フリーマン活用率</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">判断の根拠</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">パスコースの広がり</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">不確実性を圧縮するための第三者の活用</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AG-GEN-035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">プレスのトリガー練習</t>
+  </si>
+  <si>
+    <t xml:space="preserve">プレスの連動</t>
+  </si>
+  <si>
+    <t xml:space="preserve">プレスをかけるサイン（トリガー）をチームで共有し、連動したプレスを習慣化する。</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">プレスのトリガー条件（例：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">GK</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">へのバックパス）を決める</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">サイン役（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FW</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）が動いたら全員で連動</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">トリガーが発動する前に「どの条件か？」を予測して準備</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">トリガーを変えて繰り返し、適応力を高める</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">「何がトリガーだった？」「全員連動できた？」</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">トリガー認識の速さ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">全員の連動率</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">場面への適応</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">チームの集合的な予測と行動の同期</t>
   </si>
   <si>
     <t xml:space="preserve">age_group_label</t>
@@ -6142,8 +8537,8 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FF0070C0"/>
-        <rFont val="Courier New"/>
-        <family val="0"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Google Sheets</t>
@@ -6161,8 +8556,8 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FF0070C0"/>
-        <rFont val="Courier New"/>
-        <family val="0"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">=query(menu_master!A:R, "SELECT A,B,D,E,F,G,H,I,J WHERE C='elem' AND P='TRUE' ORDER BY Q", 1)</t>
@@ -6215,8 +8610,8 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FF0070C0"/>
-        <rFont val="Courier New"/>
-        <family val="0"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Google Sheets</t>
@@ -6234,8 +8629,8 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FF0070C0"/>
-        <rFont val="Courier New"/>
-        <family val="0"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">=query(menu_master!A:R, "SELECT A,B,C,E,F,G,H,I,J WHERE D='gk' AND P='TRUE' ORDER BY Q", 1)</t>
@@ -6258,8 +8653,8 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FF0070C0"/>
-        <rFont val="Courier New"/>
-        <family val="0"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Google Sheets</t>
@@ -6277,8 +8672,8 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FF0070C0"/>
-        <rFont val="Courier New"/>
-        <family val="0"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">=query(menu_master!A:R, "SELECT A,B,C,D,E,F,H,I,J WHERE G='tactic' AND P='TRUE' ORDER BY Q", 1)</t>
@@ -6331,8 +8726,8 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FF0070C0"/>
-        <rFont val="Courier New"/>
-        <family val="0"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Google Sheets</t>
@@ -6350,8 +8745,8 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FF0070C0"/>
-        <rFont val="Courier New"/>
-        <family val="0"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">=query(menu_master!A:R, "SELECT A,B,C,D,E,G,H,I,J WHERE F='P1' AND P='TRUE' ORDER BY Q", 1)</t>
@@ -6374,8 +8769,8 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FF0070C0"/>
-        <rFont val="Courier New"/>
-        <family val="0"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Google Sheets</t>
@@ -6393,8 +8788,8 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FF0070C0"/>
-        <rFont val="Courier New"/>
-        <family val="0"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">=query(menu_master!A:R, "SELECT A,B,C,D,E,F,G,H,I,J WHERE P='TRUE' ORDER BY Q", 1)</t>
@@ -6678,7 +9073,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -6736,6 +9131,12 @@
       <name val="DejaVu Sans"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="DejaVu Sans"/>
+      <family val="2"/>
     </font>
     <font>
       <b val="true"/>
@@ -6810,8 +9211,8 @@
     <font>
       <sz val="9"/>
       <color rgb="FF0070C0"/>
-      <name val="Courier New"/>
-      <family val="0"/>
+      <name val="DejaVu Sans"/>
+      <family val="2"/>
       <charset val="1"/>
     </font>
     <font>
@@ -6959,7 +9360,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="55">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -7084,11 +9485,43 @@
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -7096,11 +9529,11 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -7112,7 +9545,7 @@
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -7128,23 +9561,23 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="19" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -7514,7 +9947,7 @@
     <tabColor rgb="FF1A3A5C"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:R65"/>
+  <dimension ref="A1:R68"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16"/>
@@ -9519,7 +11952,7 @@
       <c r="J36" s="19" t="s">
         <v>317</v>
       </c>
-      <c r="K36" s="21" t="s">
+      <c r="K36" s="31" t="s">
         <v>318</v>
       </c>
       <c r="L36" s="21" t="s">
@@ -9573,10 +12006,10 @@
       <c r="J37" s="8" t="s">
         <v>325</v>
       </c>
-      <c r="K37" s="10" t="s">
+      <c r="K37" s="32" t="s">
         <v>326</v>
       </c>
-      <c r="L37" s="10" t="s">
+      <c r="L37" s="32" t="s">
         <v>327</v>
       </c>
       <c r="M37" s="10" t="s">
@@ -9910,7 +12343,7 @@
         <v>378</v>
       </c>
       <c r="O43" s="8" t="s">
-        <v>155</v>
+        <v>379</v>
       </c>
       <c r="P43" s="9" t="s">
         <v>31</v>
@@ -9924,10 +12357,10 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="18" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B44" s="19" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C44" s="20" t="s">
         <v>20</v>
@@ -9949,22 +12382,22 @@
       </c>
       <c r="I44" s="19"/>
       <c r="J44" s="19" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="K44" s="21" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="L44" s="21" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="M44" s="21" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="N44" s="21" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="O44" s="19" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="P44" s="20" t="s">
         <v>31</v>
@@ -9978,10 +12411,10 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="7" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C45" s="9" t="s">
         <v>20</v>
@@ -10003,22 +12436,22 @@
       </c>
       <c r="I45" s="8"/>
       <c r="J45" s="8" t="s">
-        <v>389</v>
-      </c>
-      <c r="K45" s="12" t="s">
         <v>390</v>
       </c>
+      <c r="K45" s="10" t="s">
+        <v>391</v>
+      </c>
       <c r="L45" s="10" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="M45" s="10" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="O45" s="8" t="s">
-        <v>179</v>
+        <v>395</v>
       </c>
       <c r="P45" s="9" t="s">
         <v>31</v>
@@ -10032,10 +12465,10 @@
     </row>
     <row r="46" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="13" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B46" s="14" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C46" s="15" t="s">
         <v>20</v>
@@ -10057,22 +12490,22 @@
       </c>
       <c r="I46" s="14"/>
       <c r="J46" s="14" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="K46" s="16" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="L46" s="16" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="M46" s="16" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="N46" s="16" t="s">
         <v>227</v>
       </c>
       <c r="O46" s="14" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="P46" s="15" t="s">
         <v>31</v>
@@ -10086,10 +12519,10 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="7" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="C47" s="9" t="s">
         <v>20</v>
@@ -10111,22 +12544,22 @@
       </c>
       <c r="I47" s="8"/>
       <c r="J47" s="8" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="K47" s="10" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="L47" s="10" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="M47" s="10" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="O47" s="8" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="P47" s="9" t="s">
         <v>31</v>
@@ -10140,10 +12573,10 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="18" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B48" s="19" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C48" s="20" t="s">
         <v>20</v>
@@ -10165,22 +12598,22 @@
       </c>
       <c r="I48" s="19"/>
       <c r="J48" s="19" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="K48" s="22" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="L48" s="21" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="M48" s="21" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="N48" s="21" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="O48" s="19" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="P48" s="20" t="s">
         <v>31</v>
@@ -10194,10 +12627,10 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="7" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C49" s="9" t="s">
         <v>20</v>
@@ -10219,22 +12652,22 @@
       </c>
       <c r="I49" s="8"/>
       <c r="J49" s="8" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="K49" s="10" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="L49" s="10" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="M49" s="10" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>378</v>
+        <v>425</v>
       </c>
       <c r="O49" s="8" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="P49" s="9" t="s">
         <v>31</v>
@@ -10248,16 +12681,16 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="18" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="B50" s="19" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="C50" s="20" t="s">
         <v>20</v>
       </c>
       <c r="D50" s="20" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="E50" s="19" t="s">
         <v>54</v>
@@ -10276,19 +12709,19 @@
         <v>104</v>
       </c>
       <c r="K50" s="21" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="L50" s="21" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="M50" s="21" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="N50" s="21" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="O50" s="19" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="P50" s="20" t="s">
         <v>31</v>
@@ -10302,16 +12735,16 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="7" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="C51" s="9" t="s">
         <v>20</v>
       </c>
       <c r="D51" s="9" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="E51" s="8" t="s">
         <v>21</v>
@@ -10327,22 +12760,22 @@
       </c>
       <c r="I51" s="8"/>
       <c r="J51" s="8" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="K51" s="10" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="L51" s="10" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="M51" s="10" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="O51" s="8" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="P51" s="9" t="s">
         <v>31</v>
@@ -10356,16 +12789,16 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="18" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="B52" s="20" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="C52" s="20" t="s">
         <v>20</v>
       </c>
       <c r="D52" s="20" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="E52" s="19" t="s">
         <v>54</v>
@@ -10381,22 +12814,22 @@
       </c>
       <c r="I52" s="19"/>
       <c r="J52" s="19" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="K52" s="21" t="s">
-        <v>443</v>
-      </c>
-      <c r="L52" s="22" t="s">
-        <v>444</v>
+        <v>446</v>
+      </c>
+      <c r="L52" s="21" t="s">
+        <v>447</v>
       </c>
       <c r="M52" s="21" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="N52" s="21" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="O52" s="19" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="P52" s="20" t="s">
         <v>31</v>
@@ -10410,16 +12843,16 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="7" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="B53" s="8" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="C53" s="9" t="s">
         <v>20</v>
       </c>
       <c r="D53" s="9" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="E53" s="8" t="s">
         <v>54</v>
@@ -10435,22 +12868,22 @@
       </c>
       <c r="I53" s="8"/>
       <c r="J53" s="8" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="K53" s="10" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="L53" s="10" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="M53" s="10" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>450</v>
+        <v>457</v>
       </c>
       <c r="O53" s="8" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="P53" s="9" t="s">
         <v>31</v>
@@ -10464,16 +12897,16 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="18" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="B54" s="19" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="C54" s="20" t="s">
         <v>20</v>
       </c>
       <c r="D54" s="20" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="E54" s="19" t="s">
         <v>43</v>
@@ -10489,22 +12922,22 @@
       </c>
       <c r="I54" s="19"/>
       <c r="J54" s="19" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="K54" s="21" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="L54" s="21" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="M54" s="21" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="N54" s="21" t="s">
         <v>170</v>
       </c>
       <c r="O54" s="19" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="P54" s="20" t="s">
         <v>31</v>
@@ -10518,16 +12951,16 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="7" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="B55" s="8" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="C55" s="9" t="s">
         <v>20</v>
       </c>
       <c r="D55" s="9" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="E55" s="8" t="s">
         <v>138</v>
@@ -10543,22 +12976,22 @@
       </c>
       <c r="I55" s="8"/>
       <c r="J55" s="8" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="K55" s="10" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="L55" s="10" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="M55" s="10" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="O55" s="8" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="P55" s="9" t="s">
         <v>31</v>
@@ -10572,16 +13005,16 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="18" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="B56" s="19" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="C56" s="20" t="s">
         <v>20</v>
       </c>
       <c r="D56" s="20" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="E56" s="19" t="s">
         <v>54</v>
@@ -10597,16 +13030,16 @@
       </c>
       <c r="I56" s="19"/>
       <c r="J56" s="19" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="K56" s="21" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="L56" s="21" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="M56" s="21" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="N56" s="21" t="s">
         <v>210</v>
@@ -10626,16 +13059,16 @@
     </row>
     <row r="57" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="7" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="B57" s="8" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="C57" s="9" t="s">
         <v>20</v>
       </c>
       <c r="D57" s="9" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="E57" s="8" t="s">
         <v>43</v>
@@ -10651,22 +13084,22 @@
       </c>
       <c r="I57" s="8"/>
       <c r="J57" s="8" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="K57" s="10" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="L57" s="10" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="M57" s="10" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="O57" s="8" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="P57" s="9" t="s">
         <v>31</v>
@@ -10680,16 +13113,16 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="18" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="B58" s="19" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="C58" s="20" t="s">
         <v>20</v>
       </c>
       <c r="D58" s="20" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="E58" s="19" t="s">
         <v>54</v>
@@ -10705,22 +13138,22 @@
       </c>
       <c r="I58" s="19"/>
       <c r="J58" s="19" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="K58" s="21" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="L58" s="21" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="M58" s="21" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="N58" s="21" t="s">
-        <v>107</v>
-      </c>
-      <c r="O58" s="19" t="s">
-        <v>491</v>
+        <v>495</v>
+      </c>
+      <c r="O58" s="33" t="s">
+        <v>496</v>
       </c>
       <c r="P58" s="20" t="s">
         <v>31</v>
@@ -10734,16 +13167,16 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="7" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="B59" s="8" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="C59" s="9" t="s">
         <v>20</v>
       </c>
       <c r="D59" s="9" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="E59" s="8" t="s">
         <v>21</v>
@@ -10759,22 +13192,22 @@
       </c>
       <c r="I59" s="8"/>
       <c r="J59" s="8" t="s">
-        <v>494</v>
-      </c>
-      <c r="K59" s="12" t="s">
-        <v>495</v>
-      </c>
-      <c r="L59" s="12" t="s">
-        <v>496</v>
+        <v>499</v>
+      </c>
+      <c r="K59" s="10" t="s">
+        <v>500</v>
+      </c>
+      <c r="L59" s="10" t="s">
+        <v>501</v>
       </c>
       <c r="M59" s="10" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="O59" s="8" t="s">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="P59" s="9" t="s">
         <v>31</v>
@@ -10788,16 +13221,16 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="13" t="s">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="B60" s="15" t="s">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="C60" s="15" t="s">
         <v>20</v>
       </c>
       <c r="D60" s="15" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="E60" s="14" t="s">
         <v>54</v>
@@ -10813,22 +13246,22 @@
       </c>
       <c r="I60" s="14"/>
       <c r="J60" s="15" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="K60" s="17" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="L60" s="17" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="M60" s="16" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="N60" s="16" t="s">
-        <v>506</v>
-      </c>
-      <c r="O60" s="14" t="s">
-        <v>507</v>
+        <v>511</v>
+      </c>
+      <c r="O60" s="34" t="s">
+        <v>512</v>
       </c>
       <c r="P60" s="15" t="s">
         <v>31</v>
@@ -10842,16 +13275,16 @@
     </row>
     <row r="61" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="7" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="B61" s="8" t="s">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="C61" s="9" t="s">
         <v>20</v>
       </c>
       <c r="D61" s="9" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="E61" s="8" t="s">
         <v>43</v>
@@ -10867,22 +13300,22 @@
       </c>
       <c r="I61" s="8"/>
       <c r="J61" s="8" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="K61" s="10" t="s">
-        <v>511</v>
-      </c>
-      <c r="L61" s="12" t="s">
-        <v>512</v>
+        <v>516</v>
+      </c>
+      <c r="L61" s="10" t="s">
+        <v>517</v>
       </c>
       <c r="M61" s="10" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="O61" s="8" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="P61" s="9" t="s">
         <v>31</v>
@@ -10896,16 +13329,16 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="13" t="s">
-        <v>516</v>
+        <v>521</v>
       </c>
       <c r="B62" s="14" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="C62" s="15" t="s">
         <v>20</v>
       </c>
       <c r="D62" s="15" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="E62" s="14" t="s">
         <v>43</v>
@@ -10921,22 +13354,22 @@
       </c>
       <c r="I62" s="14"/>
       <c r="J62" s="14" t="s">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="K62" s="16" t="s">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="L62" s="16" t="s">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="M62" s="16" t="s">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="N62" s="16" t="s">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="O62" s="14" t="s">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="P62" s="15" t="s">
         <v>31</v>
@@ -10950,16 +13383,16 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="7" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="B63" s="8" t="s">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="C63" s="9" t="s">
         <v>20</v>
       </c>
       <c r="D63" s="9" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="E63" s="8" t="s">
         <v>21</v>
@@ -10975,22 +13408,22 @@
       </c>
       <c r="I63" s="8"/>
       <c r="J63" s="8" t="s">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="K63" s="10" t="s">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="L63" s="10" t="s">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="M63" s="10" t="s">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="O63" s="8" t="s">
-        <v>531</v>
+        <v>536</v>
       </c>
       <c r="P63" s="9" t="s">
         <v>31</v>
@@ -11004,16 +13437,16 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="18" t="s">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="B64" s="19" t="s">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="C64" s="20" t="s">
         <v>20</v>
       </c>
       <c r="D64" s="20" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="E64" s="19" t="s">
         <v>43</v>
@@ -11029,22 +13462,22 @@
       </c>
       <c r="I64" s="19"/>
       <c r="J64" s="19" t="s">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="K64" s="22" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="L64" s="21" t="s">
-        <v>536</v>
+        <v>541</v>
       </c>
       <c r="M64" s="21" t="s">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="N64" s="21" t="s">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="O64" s="19" t="s">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="P64" s="20" t="s">
         <v>31</v>
@@ -11058,16 +13491,16 @@
     </row>
     <row r="65" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="7" t="s">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="B65" s="8" t="s">
-        <v>541</v>
+        <v>546</v>
       </c>
       <c r="C65" s="9" t="s">
         <v>20</v>
       </c>
       <c r="D65" s="9" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="E65" s="8" t="s">
         <v>43</v>
@@ -11083,22 +13516,22 @@
       </c>
       <c r="I65" s="8"/>
       <c r="J65" s="8" t="s">
-        <v>542</v>
+        <v>547</v>
       </c>
       <c r="K65" s="10" t="s">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="L65" s="12" t="s">
-        <v>544</v>
+        <v>549</v>
       </c>
       <c r="M65" s="10" t="s">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="O65" s="8" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="P65" s="9" t="s">
         <v>31</v>
@@ -11107,6 +13540,177 @@
         <v>640</v>
       </c>
       <c r="R65" s="9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="35" t="s">
+        <v>553</v>
+      </c>
+      <c r="B66" s="36" t="s">
+        <v>554</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E66" s="36" t="s">
+        <v>54</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="G66" s="37" t="s">
+        <v>149</v>
+      </c>
+      <c r="H66" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="I66" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="J66" s="36" t="s">
+        <v>555</v>
+      </c>
+      <c r="K66" s="36" t="s">
+        <v>556</v>
+      </c>
+      <c r="L66" s="36" t="s">
+        <v>557</v>
+      </c>
+      <c r="M66" s="36" t="s">
+        <v>558</v>
+      </c>
+      <c r="N66" s="36" t="s">
+        <v>559</v>
+      </c>
+      <c r="O66" s="36" t="s">
+        <v>560</v>
+      </c>
+      <c r="P66" s="38" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="Q66" s="1" t="n">
+        <v>650</v>
+      </c>
+      <c r="R66" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="35" t="s">
+        <v>561</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E67" s="36" t="s">
+        <v>43</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G67" s="37" t="s">
+        <v>149</v>
+      </c>
+      <c r="H67" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="I67" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="J67" s="36" t="s">
+        <v>563</v>
+      </c>
+      <c r="K67" s="36" t="s">
+        <v>564</v>
+      </c>
+      <c r="L67" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="M67" s="36" t="s">
+        <v>566</v>
+      </c>
+      <c r="N67" s="36" t="s">
+        <v>567</v>
+      </c>
+      <c r="O67" s="36" t="s">
+        <v>568</v>
+      </c>
+      <c r="P67" s="38" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="Q67" s="1" t="n">
+        <v>660</v>
+      </c>
+      <c r="R67" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="35" t="s">
+        <v>569</v>
+      </c>
+      <c r="B68" s="36" t="s">
+        <v>570</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E68" s="36" t="s">
+        <v>43</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G68" s="37" t="s">
+        <v>149</v>
+      </c>
+      <c r="H68" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="I68" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="J68" s="36" t="s">
+        <v>571</v>
+      </c>
+      <c r="K68" s="36" t="s">
+        <v>572</v>
+      </c>
+      <c r="L68" s="36" t="s">
+        <v>573</v>
+      </c>
+      <c r="M68" s="36" t="s">
+        <v>574</v>
+      </c>
+      <c r="N68" s="36" t="s">
+        <v>575</v>
+      </c>
+      <c r="O68" s="36" t="s">
+        <v>576</v>
+      </c>
+      <c r="P68" s="38" t="b">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="Q68" s="1" t="n">
+        <v>670</v>
+      </c>
+      <c r="R68" s="1" t="s">
         <v>32</v>
       </c>
     </row>
@@ -11159,173 +13763,173 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="39" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="31" t="s">
-        <v>548</v>
-      </c>
-      <c r="D1" s="31" t="s">
+      <c r="B1" s="39" t="s">
+        <v>577</v>
+      </c>
+      <c r="D1" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="31" t="s">
-        <v>549</v>
-      </c>
-      <c r="G1" s="31" t="s">
+      <c r="E1" s="39" t="s">
+        <v>578</v>
+      </c>
+      <c r="G1" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="31" t="s">
-        <v>550</v>
-      </c>
-      <c r="J1" s="31" t="s">
-        <v>551</v>
-      </c>
-      <c r="K1" s="31" t="s">
-        <v>552</v>
-      </c>
-      <c r="M1" s="31" t="s">
+      <c r="H1" s="39" t="s">
+        <v>579</v>
+      </c>
+      <c r="J1" s="39" t="s">
+        <v>580</v>
+      </c>
+      <c r="K1" s="39" t="s">
+        <v>581</v>
+      </c>
+      <c r="M1" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="N1" s="31" t="s">
-        <v>553</v>
-      </c>
-      <c r="P1" s="31" t="s">
+      <c r="N1" s="39" t="s">
+        <v>582</v>
+      </c>
+      <c r="P1" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="Q1" s="31" t="s">
-        <v>554</v>
-      </c>
-      <c r="S1" s="31" t="s">
+      <c r="Q1" s="39" t="s">
+        <v>583</v>
+      </c>
+      <c r="S1" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="T1" s="31" t="s">
-        <v>555</v>
+      <c r="T1" s="39" t="s">
+        <v>584</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="7" t="s">
-        <v>556</v>
+        <v>585</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>557</v>
+        <v>586</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>299</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>558</v>
-      </c>
-      <c r="G2" s="32" t="s">
+        <v>587</v>
+      </c>
+      <c r="G2" s="40" t="s">
         <v>21</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>559</v>
+        <v>588</v>
       </c>
       <c r="J2" s="7" t="s">
         <v>55</v>
       </c>
       <c r="K2" s="8" t="s">
-        <v>560</v>
+        <v>589</v>
       </c>
       <c r="M2" s="7" t="s">
         <v>23</v>
       </c>
       <c r="N2" s="8" t="s">
-        <v>561</v>
+        <v>590</v>
       </c>
       <c r="P2" s="7" t="s">
         <v>45</v>
       </c>
       <c r="Q2" s="8" t="s">
-        <v>562</v>
+        <v>591</v>
       </c>
       <c r="S2" s="7" t="s">
         <v>31</v>
       </c>
       <c r="T2" s="8" t="s">
-        <v>563</v>
+        <v>592</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="s">
-        <v>564</v>
+        <v>593</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>565</v>
+        <v>594</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>365</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>566</v>
-      </c>
-      <c r="G3" s="32" t="s">
+        <v>595</v>
+      </c>
+      <c r="G3" s="40" t="s">
         <v>89</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>567</v>
+        <v>596</v>
       </c>
       <c r="J3" s="7" t="s">
         <v>22</v>
       </c>
       <c r="K3" s="8" t="s">
-        <v>568</v>
+        <v>597</v>
       </c>
       <c r="M3" s="7" t="s">
         <v>80</v>
       </c>
       <c r="N3" s="8" t="s">
-        <v>569</v>
+        <v>598</v>
       </c>
       <c r="P3" s="7" t="s">
         <v>24</v>
       </c>
       <c r="Q3" s="8" t="s">
-        <v>570</v>
+        <v>599</v>
       </c>
       <c r="S3" s="7" t="s">
-        <v>571</v>
+        <v>600</v>
       </c>
       <c r="T3" s="8" t="s">
-        <v>572</v>
+        <v>601</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>573</v>
+        <v>602</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>574</v>
+        <v>603</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>575</v>
-      </c>
-      <c r="G4" s="32" t="s">
+        <v>604</v>
+      </c>
+      <c r="G4" s="40" t="s">
         <v>264</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>576</v>
+        <v>605</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>139</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>577</v>
+        <v>606</v>
       </c>
       <c r="M4" s="7" t="s">
         <v>149</v>
       </c>
       <c r="N4" s="8" t="s">
-        <v>578</v>
+        <v>607</v>
       </c>
       <c r="P4" s="7" t="s">
         <v>90</v>
       </c>
       <c r="Q4" s="8" t="s">
-        <v>579</v>
+        <v>608</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11333,37 +13937,37 @@
         <v>20</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>580</v>
+        <v>609</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>581</v>
-      </c>
-      <c r="G5" s="32" t="s">
+        <v>610</v>
+      </c>
+      <c r="G5" s="40" t="s">
         <v>138</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>582</v>
+        <v>611</v>
       </c>
       <c r="J5" s="7" t="s">
         <v>316</v>
       </c>
       <c r="K5" s="8" t="s">
-        <v>583</v>
+        <v>612</v>
       </c>
       <c r="M5" s="7" t="s">
         <v>214</v>
       </c>
       <c r="N5" s="8" t="s">
-        <v>584</v>
+        <v>613</v>
       </c>
       <c r="P5" s="7" t="s">
         <v>255</v>
       </c>
       <c r="Q5" s="8" t="s">
-        <v>585</v>
+        <v>614</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11371,53 +13975,53 @@
         <v>20</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>586</v>
-      </c>
-      <c r="G6" s="32" t="s">
+        <v>615</v>
+      </c>
+      <c r="G6" s="40" t="s">
         <v>43</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>587</v>
+        <v>616</v>
       </c>
       <c r="J6" s="7" t="s">
         <v>148</v>
       </c>
       <c r="K6" s="8" t="s">
-        <v>588</v>
+        <v>617</v>
       </c>
       <c r="M6" s="7" t="s">
         <v>265</v>
       </c>
       <c r="N6" s="8" t="s">
-        <v>589</v>
+        <v>618</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G7" s="32" t="s">
+      <c r="G7" s="40" t="s">
         <v>54</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>590</v>
+        <v>619</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>591</v>
+        <v>620</v>
       </c>
       <c r="K7" s="8" t="s">
-        <v>592</v>
+        <v>621</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G8" s="32" t="s">
+      <c r="G8" s="40" t="s">
         <v>282</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>593</v>
+        <v>622</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>594</v>
+        <v>623</v>
       </c>
       <c r="K8" s="8" t="s">
-        <v>595</v>
+        <v>624</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11425,23 +14029,23 @@
         <v>283</v>
       </c>
       <c r="K9" s="8" t="s">
-        <v>596</v>
+        <v>625</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J10" s="7" t="s">
-        <v>597</v>
+        <v>626</v>
       </c>
       <c r="K10" s="8" t="s">
-        <v>598</v>
+        <v>627</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J11" s="7" t="s">
-        <v>599</v>
+        <v>628</v>
       </c>
       <c r="K11" s="8" t="s">
-        <v>600</v>
+        <v>629</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11449,7 +14053,7 @@
         <v>44</v>
       </c>
       <c r="K12" s="8" t="s">
-        <v>601</v>
+        <v>630</v>
       </c>
     </row>
   </sheetData>
@@ -11482,560 +14086,560 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="33" t="s">
-        <v>602</v>
-      </c>
-      <c r="B1" s="33" t="s">
-        <v>603</v>
-      </c>
-      <c r="C1" s="33" t="s">
+      <c r="A1" s="41" t="s">
+        <v>631</v>
+      </c>
+      <c r="B1" s="41" t="s">
+        <v>632</v>
+      </c>
+      <c r="C1" s="41" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="33" t="s">
+      <c r="D1" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="33" t="s">
-        <v>604</v>
-      </c>
-      <c r="F1" s="33" t="s">
-        <v>605</v>
-      </c>
-      <c r="G1" s="33" t="s">
+      <c r="E1" s="41" t="s">
+        <v>633</v>
+      </c>
+      <c r="F1" s="41" t="s">
+        <v>634</v>
+      </c>
+      <c r="G1" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="H1" s="33" t="s">
-        <v>606</v>
+      <c r="H1" s="41" t="s">
+        <v>635</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="10.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="34" t="s">
-        <v>607</v>
-      </c>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
-      <c r="H2" s="34"/>
+      <c r="A2" s="42" t="s">
+        <v>636</v>
+      </c>
+      <c r="B2" s="42"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="42"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="35" t="s">
-        <v>608</v>
-      </c>
-      <c r="B3" s="36" t="s">
-        <v>609</v>
-      </c>
-      <c r="C3" s="37" t="s">
-        <v>556</v>
-      </c>
-      <c r="D3" s="37" t="s">
+      <c r="A3" s="43" t="s">
+        <v>637</v>
+      </c>
+      <c r="B3" s="44" t="s">
+        <v>638</v>
+      </c>
+      <c r="C3" s="45" t="s">
+        <v>585</v>
+      </c>
+      <c r="D3" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="E3" s="36" t="n">
+      <c r="E3" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="F3" s="36" t="n">
+      <c r="F3" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="G3" s="37" t="s">
+      <c r="G3" s="45" t="s">
         <v>41</v>
       </c>
-      <c r="H3" s="36" t="s">
-        <v>610</v>
+      <c r="H3" s="44" t="s">
+        <v>639</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="35" t="s">
-        <v>608</v>
-      </c>
-      <c r="B4" s="36" t="s">
-        <v>609</v>
-      </c>
-      <c r="C4" s="37" t="s">
-        <v>556</v>
-      </c>
-      <c r="D4" s="37" t="s">
+      <c r="A4" s="43" t="s">
+        <v>637</v>
+      </c>
+      <c r="B4" s="44" t="s">
+        <v>638</v>
+      </c>
+      <c r="C4" s="45" t="s">
+        <v>585</v>
+      </c>
+      <c r="D4" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="E4" s="36" t="n">
+      <c r="E4" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="F4" s="36" t="n">
+      <c r="F4" s="44" t="n">
         <v>2</v>
       </c>
-      <c r="G4" s="37" t="s">
+      <c r="G4" s="45" t="s">
         <v>52</v>
       </c>
-      <c r="H4" s="36" t="s">
-        <v>611</v>
+      <c r="H4" s="44" t="s">
+        <v>640</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="35" t="s">
-        <v>608</v>
-      </c>
-      <c r="B5" s="36" t="s">
-        <v>609</v>
-      </c>
-      <c r="C5" s="37" t="s">
-        <v>556</v>
-      </c>
-      <c r="D5" s="37" t="s">
+      <c r="A5" s="43" t="s">
+        <v>637</v>
+      </c>
+      <c r="B5" s="44" t="s">
+        <v>638</v>
+      </c>
+      <c r="C5" s="45" t="s">
+        <v>585</v>
+      </c>
+      <c r="D5" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="E5" s="36" t="n">
+      <c r="E5" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="F5" s="36" t="n">
+      <c r="F5" s="44" t="n">
         <v>3</v>
       </c>
-      <c r="G5" s="37" t="s">
+      <c r="G5" s="45" t="s">
         <v>78</v>
       </c>
-      <c r="H5" s="36" t="s">
-        <v>612</v>
+      <c r="H5" s="44" t="s">
+        <v>641</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="35" t="s">
-        <v>608</v>
-      </c>
-      <c r="B6" s="36" t="s">
-        <v>609</v>
-      </c>
-      <c r="C6" s="37" t="s">
-        <v>556</v>
-      </c>
-      <c r="D6" s="37" t="s">
+      <c r="A6" s="43" t="s">
+        <v>637</v>
+      </c>
+      <c r="B6" s="44" t="s">
+        <v>638</v>
+      </c>
+      <c r="C6" s="45" t="s">
+        <v>585</v>
+      </c>
+      <c r="D6" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="E6" s="36" t="n">
+      <c r="E6" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="F6" s="36" t="n">
+      <c r="F6" s="44" t="n">
         <v>4</v>
       </c>
-      <c r="G6" s="37" t="s">
+      <c r="G6" s="45" t="s">
         <v>156</v>
       </c>
-      <c r="H6" s="37" t="s">
-        <v>613</v>
+      <c r="H6" s="45" t="s">
+        <v>642</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="35" t="s">
-        <v>608</v>
-      </c>
-      <c r="B7" s="36" t="s">
-        <v>609</v>
-      </c>
-      <c r="C7" s="37" t="s">
-        <v>556</v>
-      </c>
-      <c r="D7" s="37" t="s">
+      <c r="A7" s="43" t="s">
+        <v>637</v>
+      </c>
+      <c r="B7" s="44" t="s">
+        <v>638</v>
+      </c>
+      <c r="C7" s="45" t="s">
+        <v>585</v>
+      </c>
+      <c r="D7" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="36" t="n">
+      <c r="E7" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="F7" s="36" t="n">
+      <c r="F7" s="44" t="n">
         <v>5</v>
       </c>
-      <c r="G7" s="37" t="s">
+      <c r="G7" s="45" t="s">
         <v>272</v>
       </c>
-      <c r="H7" s="36" t="s">
+      <c r="H7" s="44" t="s">
         <v>273</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="35" t="s">
-        <v>608</v>
-      </c>
-      <c r="B8" s="36" t="s">
-        <v>609</v>
-      </c>
-      <c r="C8" s="37" t="s">
-        <v>556</v>
-      </c>
-      <c r="D8" s="37" t="s">
+      <c r="A8" s="43" t="s">
+        <v>637</v>
+      </c>
+      <c r="B8" s="44" t="s">
+        <v>638</v>
+      </c>
+      <c r="C8" s="45" t="s">
+        <v>585</v>
+      </c>
+      <c r="D8" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="36" t="n">
+      <c r="E8" s="44" t="n">
         <v>2</v>
       </c>
-      <c r="F8" s="36" t="n">
+      <c r="F8" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="G8" s="37" t="s">
+      <c r="G8" s="45" t="s">
         <v>62</v>
       </c>
-      <c r="H8" s="36" t="s">
-        <v>614</v>
+      <c r="H8" s="44" t="s">
+        <v>643</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="35" t="s">
-        <v>608</v>
-      </c>
-      <c r="B9" s="36" t="s">
-        <v>609</v>
-      </c>
-      <c r="C9" s="37" t="s">
-        <v>556</v>
-      </c>
-      <c r="D9" s="37" t="s">
+      <c r="A9" s="43" t="s">
+        <v>637</v>
+      </c>
+      <c r="B9" s="44" t="s">
+        <v>638</v>
+      </c>
+      <c r="C9" s="45" t="s">
+        <v>585</v>
+      </c>
+      <c r="D9" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="36" t="n">
+      <c r="E9" s="44" t="n">
         <v>2</v>
       </c>
-      <c r="F9" s="36" t="n">
+      <c r="F9" s="44" t="n">
         <v>2</v>
       </c>
-      <c r="G9" s="37" t="s">
+      <c r="G9" s="45" t="s">
         <v>87</v>
       </c>
-      <c r="H9" s="36" t="s">
-        <v>615</v>
+      <c r="H9" s="44" t="s">
+        <v>644</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="35" t="s">
-        <v>608</v>
-      </c>
-      <c r="B10" s="36" t="s">
-        <v>609</v>
-      </c>
-      <c r="C10" s="37" t="s">
-        <v>556</v>
-      </c>
-      <c r="D10" s="37" t="s">
+      <c r="A10" s="43" t="s">
+        <v>637</v>
+      </c>
+      <c r="B10" s="44" t="s">
+        <v>638</v>
+      </c>
+      <c r="C10" s="45" t="s">
+        <v>585</v>
+      </c>
+      <c r="D10" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="36" t="n">
+      <c r="E10" s="44" t="n">
         <v>2</v>
       </c>
-      <c r="F10" s="36" t="n">
+      <c r="F10" s="44" t="n">
         <v>3</v>
       </c>
-      <c r="G10" s="37" t="s">
+      <c r="G10" s="45" t="s">
         <v>229</v>
       </c>
-      <c r="H10" s="36" t="s">
+      <c r="H10" s="44" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="35" t="s">
-        <v>608</v>
-      </c>
-      <c r="B11" s="36" t="s">
-        <v>609</v>
-      </c>
-      <c r="C11" s="37" t="s">
-        <v>556</v>
-      </c>
-      <c r="D11" s="37" t="s">
+      <c r="A11" s="43" t="s">
+        <v>637</v>
+      </c>
+      <c r="B11" s="44" t="s">
+        <v>638</v>
+      </c>
+      <c r="C11" s="45" t="s">
+        <v>585</v>
+      </c>
+      <c r="D11" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="36" t="n">
+      <c r="E11" s="44" t="n">
         <v>2</v>
       </c>
-      <c r="F11" s="36" t="n">
+      <c r="F11" s="44" t="n">
         <v>4</v>
       </c>
-      <c r="G11" s="37" t="s">
+      <c r="G11" s="45" t="s">
         <v>164</v>
       </c>
-      <c r="H11" s="36" t="s">
-        <v>616</v>
+      <c r="H11" s="44" t="s">
+        <v>645</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="35" t="s">
-        <v>608</v>
-      </c>
-      <c r="B12" s="36" t="s">
-        <v>609</v>
-      </c>
-      <c r="C12" s="37" t="s">
-        <v>556</v>
-      </c>
-      <c r="D12" s="37" t="s">
+      <c r="A12" s="43" t="s">
+        <v>637</v>
+      </c>
+      <c r="B12" s="44" t="s">
+        <v>638</v>
+      </c>
+      <c r="C12" s="45" t="s">
+        <v>585</v>
+      </c>
+      <c r="D12" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="E12" s="36" t="n">
+      <c r="E12" s="44" t="n">
         <v>2</v>
       </c>
-      <c r="F12" s="36" t="n">
+      <c r="F12" s="44" t="n">
         <v>5</v>
       </c>
-      <c r="G12" s="37" t="s">
+      <c r="G12" s="45" t="s">
         <v>272</v>
       </c>
-      <c r="H12" s="36" t="s">
+      <c r="H12" s="44" t="s">
         <v>273</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="35" t="s">
-        <v>608</v>
-      </c>
-      <c r="B13" s="36" t="s">
-        <v>609</v>
-      </c>
-      <c r="C13" s="37" t="s">
-        <v>556</v>
-      </c>
-      <c r="D13" s="37" t="s">
+      <c r="A13" s="43" t="s">
+        <v>637</v>
+      </c>
+      <c r="B13" s="44" t="s">
+        <v>638</v>
+      </c>
+      <c r="C13" s="45" t="s">
+        <v>585</v>
+      </c>
+      <c r="D13" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="E13" s="36" t="n">
+      <c r="E13" s="44" t="n">
         <v>3</v>
       </c>
-      <c r="F13" s="36" t="n">
+      <c r="F13" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="G13" s="37" t="s">
+      <c r="G13" s="45" t="s">
         <v>70</v>
       </c>
-      <c r="H13" s="36" t="s">
-        <v>617</v>
+      <c r="H13" s="44" t="s">
+        <v>646</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="35" t="s">
-        <v>608</v>
-      </c>
-      <c r="B14" s="36" t="s">
-        <v>609</v>
-      </c>
-      <c r="C14" s="37" t="s">
-        <v>556</v>
-      </c>
-      <c r="D14" s="37" t="s">
+      <c r="A14" s="43" t="s">
+        <v>637</v>
+      </c>
+      <c r="B14" s="44" t="s">
+        <v>638</v>
+      </c>
+      <c r="C14" s="45" t="s">
+        <v>585</v>
+      </c>
+      <c r="D14" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="E14" s="36" t="n">
+      <c r="E14" s="44" t="n">
         <v>3</v>
       </c>
-      <c r="F14" s="36" t="n">
+      <c r="F14" s="44" t="n">
         <v>2</v>
       </c>
-      <c r="G14" s="37" t="s">
+      <c r="G14" s="45" t="s">
         <v>97</v>
       </c>
-      <c r="H14" s="36" t="s">
-        <v>618</v>
+      <c r="H14" s="44" t="s">
+        <v>647</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="35" t="s">
-        <v>608</v>
-      </c>
-      <c r="B15" s="36" t="s">
-        <v>609</v>
-      </c>
-      <c r="C15" s="37" t="s">
-        <v>556</v>
-      </c>
-      <c r="D15" s="37" t="s">
+      <c r="A15" s="43" t="s">
+        <v>637</v>
+      </c>
+      <c r="B15" s="44" t="s">
+        <v>638</v>
+      </c>
+      <c r="C15" s="45" t="s">
+        <v>585</v>
+      </c>
+      <c r="D15" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="E15" s="36" t="n">
+      <c r="E15" s="44" t="n">
         <v>3</v>
       </c>
-      <c r="F15" s="36" t="n">
+      <c r="F15" s="44" t="n">
         <v>3</v>
       </c>
-      <c r="G15" s="37" t="s">
+      <c r="G15" s="45" t="s">
         <v>146</v>
       </c>
-      <c r="H15" s="36" t="s">
+      <c r="H15" s="44" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="35" t="s">
-        <v>608</v>
-      </c>
-      <c r="B16" s="36" t="s">
-        <v>609</v>
-      </c>
-      <c r="C16" s="37" t="s">
-        <v>556</v>
-      </c>
-      <c r="D16" s="37" t="s">
+      <c r="A16" s="43" t="s">
+        <v>637</v>
+      </c>
+      <c r="B16" s="44" t="s">
+        <v>638</v>
+      </c>
+      <c r="C16" s="45" t="s">
+        <v>585</v>
+      </c>
+      <c r="D16" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="E16" s="36" t="n">
+      <c r="E16" s="44" t="n">
         <v>3</v>
       </c>
-      <c r="F16" s="36" t="n">
+      <c r="F16" s="44" t="n">
         <v>4</v>
       </c>
-      <c r="G16" s="37" t="s">
+      <c r="G16" s="45" t="s">
         <v>156</v>
       </c>
-      <c r="H16" s="37" t="s">
+      <c r="H16" s="45" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="35" t="s">
-        <v>608</v>
-      </c>
-      <c r="B17" s="36" t="s">
-        <v>609</v>
-      </c>
-      <c r="C17" s="37" t="s">
-        <v>556</v>
-      </c>
-      <c r="D17" s="37" t="s">
+      <c r="A17" s="43" t="s">
+        <v>637</v>
+      </c>
+      <c r="B17" s="44" t="s">
+        <v>638</v>
+      </c>
+      <c r="C17" s="45" t="s">
+        <v>585</v>
+      </c>
+      <c r="D17" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="E17" s="36" t="n">
+      <c r="E17" s="44" t="n">
         <v>3</v>
       </c>
-      <c r="F17" s="36" t="n">
+      <c r="F17" s="44" t="n">
         <v>5</v>
       </c>
-      <c r="G17" s="37" t="s">
+      <c r="G17" s="45" t="s">
         <v>290</v>
       </c>
-      <c r="H17" s="36" t="s">
+      <c r="H17" s="44" t="s">
         <v>291</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="38" t="s">
-        <v>619</v>
-      </c>
-      <c r="B18" s="39" t="s">
-        <v>620</v>
-      </c>
-      <c r="C18" s="39" t="s">
+      <c r="A18" s="46" t="s">
+        <v>648</v>
+      </c>
+      <c r="B18" s="47" t="s">
+        <v>649</v>
+      </c>
+      <c r="C18" s="47" t="s">
         <v>20</v>
       </c>
-      <c r="D18" s="39" t="s">
+      <c r="D18" s="47" t="s">
         <v>299</v>
       </c>
-      <c r="E18" s="39" t="n">
+      <c r="E18" s="47" t="n">
         <v>1</v>
       </c>
-      <c r="F18" s="39" t="n">
+      <c r="F18" s="47" t="n">
         <v>1</v>
       </c>
-      <c r="G18" s="39" t="s">
+      <c r="G18" s="47" t="s">
         <v>33</v>
       </c>
-      <c r="H18" s="40" t="s">
+      <c r="H18" s="48" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="38" t="s">
-        <v>619</v>
-      </c>
-      <c r="B19" s="39" t="s">
-        <v>620</v>
-      </c>
-      <c r="C19" s="39" t="s">
+      <c r="A19" s="46" t="s">
+        <v>648</v>
+      </c>
+      <c r="B19" s="47" t="s">
+        <v>649</v>
+      </c>
+      <c r="C19" s="47" t="s">
         <v>20</v>
       </c>
-      <c r="D19" s="39" t="s">
+      <c r="D19" s="47" t="s">
         <v>299</v>
       </c>
-      <c r="E19" s="40" t="n">
+      <c r="E19" s="48" t="n">
         <v>1</v>
       </c>
-      <c r="F19" s="40" t="n">
+      <c r="F19" s="48" t="n">
         <v>2</v>
       </c>
-      <c r="G19" s="39" t="s">
+      <c r="G19" s="47" t="s">
         <v>297</v>
       </c>
-      <c r="H19" s="40" t="s">
-        <v>621</v>
+      <c r="H19" s="48" t="s">
+        <v>650</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="38" t="s">
-        <v>619</v>
-      </c>
-      <c r="B20" s="39" t="s">
-        <v>620</v>
-      </c>
-      <c r="C20" s="39" t="s">
+      <c r="A20" s="46" t="s">
+        <v>648</v>
+      </c>
+      <c r="B20" s="47" t="s">
+        <v>649</v>
+      </c>
+      <c r="C20" s="47" t="s">
         <v>20</v>
       </c>
-      <c r="D20" s="39" t="s">
+      <c r="D20" s="47" t="s">
         <v>299</v>
       </c>
-      <c r="E20" s="40" t="n">
+      <c r="E20" s="48" t="n">
         <v>1</v>
       </c>
-      <c r="F20" s="40" t="n">
+      <c r="F20" s="48" t="n">
         <v>3</v>
       </c>
-      <c r="G20" s="39" t="s">
+      <c r="G20" s="47" t="s">
         <v>306</v>
       </c>
-      <c r="H20" s="40" t="s">
-        <v>622</v>
+      <c r="H20" s="48" t="s">
+        <v>651</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="38" t="s">
-        <v>619</v>
-      </c>
-      <c r="B21" s="39" t="s">
-        <v>620</v>
-      </c>
-      <c r="C21" s="39" t="s">
+      <c r="A21" s="46" t="s">
+        <v>648</v>
+      </c>
+      <c r="B21" s="47" t="s">
+        <v>649</v>
+      </c>
+      <c r="C21" s="47" t="s">
         <v>20</v>
       </c>
-      <c r="D21" s="39" t="s">
+      <c r="D21" s="47" t="s">
         <v>299</v>
       </c>
-      <c r="E21" s="40" t="n">
+      <c r="E21" s="48" t="n">
         <v>1</v>
       </c>
-      <c r="F21" s="40" t="n">
+      <c r="F21" s="48" t="n">
         <v>4</v>
       </c>
-      <c r="G21" s="39" t="s">
+      <c r="G21" s="47" t="s">
         <v>355</v>
       </c>
-      <c r="H21" s="40" t="s">
-        <v>623</v>
+      <c r="H21" s="48" t="s">
+        <v>652</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="38" t="s">
-        <v>619</v>
-      </c>
-      <c r="B22" s="39" t="s">
-        <v>620</v>
-      </c>
-      <c r="C22" s="39" t="s">
+      <c r="A22" s="46" t="s">
+        <v>648</v>
+      </c>
+      <c r="B22" s="47" t="s">
+        <v>649</v>
+      </c>
+      <c r="C22" s="47" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="39" t="s">
+      <c r="D22" s="47" t="s">
         <v>299</v>
       </c>
-      <c r="E22" s="40" t="n">
+      <c r="E22" s="48" t="n">
         <v>1</v>
       </c>
-      <c r="F22" s="40" t="n">
+      <c r="F22" s="48" t="n">
         <v>5</v>
       </c>
-      <c r="G22" s="39" t="s">
+      <c r="G22" s="47" t="s">
         <v>272</v>
       </c>
-      <c r="H22" s="40" t="s">
+      <c r="H22" s="48" t="s">
         <v>273</v>
       </c>
     </row>
@@ -12068,109 +14672,109 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="41" t="s">
-        <v>624</v>
+      <c r="A1" s="49" t="s">
+        <v>653</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="42"/>
+      <c r="A3" s="50"/>
     </row>
     <row r="4" customFormat="false" ht="11.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="43" t="s">
-        <v>625</v>
+      <c r="A4" s="51" t="s">
+        <v>654</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="42"/>
+      <c r="A5" s="50"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="44" t="s">
-        <v>626</v>
+      <c r="A6" s="52" t="s">
+        <v>655</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="45" t="s">
-        <v>627</v>
+      <c r="A7" s="53" t="s">
+        <v>656</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="42"/>
+      <c r="A8" s="50"/>
     </row>
     <row r="9" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="44" t="s">
-        <v>628</v>
+      <c r="A9" s="52" t="s">
+        <v>657</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="45" t="s">
-        <v>629</v>
+      <c r="A10" s="53" t="s">
+        <v>658</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="42"/>
+      <c r="A11" s="50"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="44" t="s">
-        <v>630</v>
+      <c r="A12" s="52" t="s">
+        <v>659</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="45" t="s">
-        <v>631</v>
+      <c r="A13" s="53" t="s">
+        <v>660</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="42"/>
+      <c r="A14" s="50"/>
     </row>
     <row r="15" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="44" t="s">
-        <v>632</v>
+      <c r="A15" s="52" t="s">
+        <v>661</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="45" t="s">
-        <v>633</v>
+      <c r="A16" s="53" t="s">
+        <v>662</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="42"/>
+      <c r="A17" s="50"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="44" t="s">
-        <v>634</v>
+      <c r="A18" s="52" t="s">
+        <v>663</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="45" t="s">
-        <v>635</v>
+      <c r="A19" s="53" t="s">
+        <v>664</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="42"/>
+      <c r="A20" s="50"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="46" t="s">
-        <v>636</v>
+      <c r="A21" s="54" t="s">
+        <v>665</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="44" t="s">
-        <v>637</v>
+      <c r="A22" s="52" t="s">
+        <v>666</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="11.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="43" t="s">
-        <v>638</v>
+      <c r="A23" s="51" t="s">
+        <v>667</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="11.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="43" t="s">
-        <v>639</v>
+      <c r="A24" s="51" t="s">
+        <v>668</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="11.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="43" t="s">
-        <v>640</v>
+      <c r="A25" s="51" t="s">
+        <v>669</v>
       </c>
     </row>
   </sheetData>
